--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_18.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_18.xlsx
@@ -650,8 +650,8 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>1</v>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1128,8 +1128,8 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1517,9 +1517,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1652,9 +1652,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
